--- a/appointments.xlsx
+++ b/appointments.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,4565 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>synced_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DRX-196</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>690115-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>แอฟ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>นมเย็น</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DRX-198</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>690116-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>รมณา</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ข้าวจ้าว</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DRX-200</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>690117-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>จุฑาทิพย์ เสลาหอม</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>มูมู่ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DRX-201</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>690117-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>จุฑาทิพย์ เสลาหอม</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>มูมู่ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (รวมแมว (2/3) + พิษสุนัขบ้า (1/2))</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DRX-498</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>จรัสศรี จันทพย์วงษ์</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ไซเรน</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจแผล</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DRX-523</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>690260-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>อร</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ต้าว</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DRX-197</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>690116-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>รมณา</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ข้าวจ้าว</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DRX-203</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>พัชราภรณ์ เอกเผ่าพันธุ์</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ทิกเกอร์</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า ( พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DRX-515</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>690262-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>นาตยา โพธิ์ม่วง</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>หมา</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DRX-208</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>690120-1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>จำเนียร เศรษฐบุตร</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>แซลม่อน</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DRX-217</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>690122-1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>วิทวัส ศรีลำไย</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>โอริโอ้</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DRX-477</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>690212-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ชรารินทร์ ลิ้มชัยโรจน์</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>แดง</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตัดไหม (ถอดแม็ก)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DRX-478</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>690241-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>สุทธินันท์ มุสิกาวัน</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ชีต้า</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (หูอักเสบ)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DRX-528</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>690233-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ชันสิทธ์ แช่มมินดา</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DRX-535</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>690260-1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>อร</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ต้าว</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ฉีดยา</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DRX-215</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>690123-1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>บี</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ญาญ่า</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนรวม 5 โรค (5 โรค (2/2))</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DRX-483</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>พัชราภรณ์ เอกเผ่าพันธุ์</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ทิกเกอร์</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ฉี่เป็นมูกๆ)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DRX-488</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>690213-1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ชนิดา ตระการนิธิ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>บะหมี่</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจเลือด (recheck CBC)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DRX-238</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>690127-5</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>วิลเลี่ยม</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP,สอบถามเพิ่มด้วยว่าวัคซีนครบเมื่อรัย)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DRX-228</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>690127-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>จัสติน</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DRX-485</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>690245-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>พิสิทธิ์    พนารัตนะโสรพ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ฮันเตอร์</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (recheck CCV/CPV test kit)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DRX-230</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>690127-2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>โทมัส</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DRX-234</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>690127-3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>แพททริค</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DRX-237</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>690127-4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>เบลล่า</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DRX-240</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>690127-6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>เมมโมรี่</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DRX-256</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>690027-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>นิภารัตน์ บัวพรม</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ไข่เจียว (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DRX-536</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>690274-1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>บุหลัน สิงขรรักษ์</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DRX-552</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>690268-1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ณัฐพงษ์ ริ้วทองชุม</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>เจ้าสัว</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DRX-469</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>690203-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>กาญ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>อ้อน</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DRX-255</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>690027-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>นิภารัตน์ บัวพรม</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ไข่เจียว (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DRX-259</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>690134-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>กฤตยา พิศุทธิภัทรา</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>แดดดี</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DRX-260</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>690136-1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ลูกนัท</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>มีอาร์</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DRX-261</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>690136-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ลูกนัท</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>มีอาร์</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (รวมแมว (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DRX-521</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>690222-1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ปัทมิษฏ์ สุวรรณวัฒนะ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ชาบู</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DRX-484</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ปรารถนา ไวปัญญา</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>เหมย (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (เชื้อรา)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DRX-499</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>จรัสศรี จันทพย์วงษ์</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ไซเรน</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตัดไหม</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DRX-508</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>690102-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ปัญญา  เหล็กดี</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>กุชชี่</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการท้องเสีย</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DRX-267</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>กาแฟ</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DRX-298</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>กาแฟ</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนลิวคิเมียแมว (ลิวคีเมีย (1/2) + test FeLV)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DRX-509</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>690257-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>สุณิสา</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>โชคดี</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจเลือด (cbc+ chem5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DRX-522</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>690217-1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>สงวน อินทร์รักษ์</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ชาบู</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>จ่ายยา — **รับยาพยาธิในเม็ดเลือดต่อเนื่อง</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DRX-269</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>690131-1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>นมสด</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DRX-524</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>690187-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ธนัชญา แซ่มี</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ปีเตอร์</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DRX-276</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>690144-1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ธนพล แทนประชา</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ตัวเล็ก</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — Ultrasound (ตรวจท้อง)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DRX-537</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>690274-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>บุหลัน สิงขรรักษ์</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตัดไหม</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DRX-293</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>690157-1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ภากร สังข์ทอง</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>จิ๊กโก๋ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DRX-538</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>690239-1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>นิลภวิษย์ ทับทอง</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ฟ้า</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนไข้หัดและหวัดแมว (วัคซีน,ถ่ายพยาธิ,หยดยา,ดูอาการขา)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DRX-292</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>690157-1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ภากร สังข์ทอง</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>จิ๊กโก๋ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (1/2))</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DRX-300</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>690162-1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ชาเย็น</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DRX-301</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>690162-1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ชาเย็น</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DRX-309</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>690007-1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>สุชาวดี ชาติกานนท์</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DRX-295</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>690159-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>พรพรรณ ณัฐวุฒิ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>หมูแดง</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DRX-299</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>690160-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ธนากร เจริญธนารัตน์</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>โพเนีย</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DRX-303</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>690162-2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>สแกมเมอร์</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DRX-304</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>690162-2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>สแกมเมอร์</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2)+ พิษสุนัข (2/2))</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DRX-320</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>690171-2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ไดม่อน</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DRX-321</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>690171-2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ไดม่อน</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DRX-323</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>690171-1</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DRX-329</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>690178-1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>มะยม (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DRX-322</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>690171-1</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DRX-328</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>690178-1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>มะยม (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DRX-377</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>690206-2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>สุฐิษา ธนาการกิตติสุข</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>นีออน</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — X-ray (ตรวจท้อง)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DRX-516</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>690092-1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ธนภรณ์</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ทองมา</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DRX-7</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>690002-1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ศิริลักษณ์</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>มะเหมี่ยว</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ,ตรวจเลือด (recheck CBC+ เคมี 5 ค่า)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DRX-357</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>690196-1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>อนัญญา เทียนธนะวัฒธ์</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ฮันนี่</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — X-ray</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DRX-64</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>690038-2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ขุมทรัพย์</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DRX-65</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>690038-1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>โยดา</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DRX-69</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>690043-1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>รื่นรมย์ เหรียญทอง</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>สองสี</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DRX-81</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>690039-1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>อาร์ม</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>สาคู</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DRX-85</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>690026-2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ญานิศา แรงจันทร์</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ชิโร่ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DRX-87</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>690056-1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>อรธิมา เอกจีน</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ไอโชค</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (BVT,DW)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DRX-110</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>690067-1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ไก่</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>อั่งเปา</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DRX-117</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>690072-1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ปิ่นแก้ว</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>มาโร</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DRX-126</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>690076-1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>อรพรรณ  ขำสุวรรณ</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>น้องถุงเงิน</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DRX-142</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>690082-1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ประชุม คุณท้าวเทียม</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>มีบุญ</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DRX-151</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>690096-1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>กฤตยา วิเชียรพาย</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ซาร่า</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DRX-161</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>690100-1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>พิสิทธิ์    สามกองงาม</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>กิมจิ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DRX-159</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>690100-2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>พิสิทธิ์    สามกองงาม</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>โซจู</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DRX-163</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>690056-2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>อรธิมา เอกจีน</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>เฉาก๊วย</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DRX-164</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>690056-3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>อรธิมา เอกจีน</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>พาดกลอน</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DRX-174</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>690056-4</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>อรธิมา เอกจีน</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>บี1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DRX-180</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>690042-2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>วราฤทธิ์ บัวโต</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ดั๊ก</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DRX-172</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>690056-5</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>อรธิมา เอกจีน</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>บี2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DRX-191</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>690009-6</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ธนาวดี เมธา</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ปลาหมึก</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DRX-210</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>690064-2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>พลูโต</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DRX-211</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>690064-3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ชาแนล</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DRX-212</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>690064-4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>เนปจูน</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DRX-214</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>690064-6</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>กาแฟ</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DRX-209</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>690064-1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ลาคอส</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DRX-213</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>690064-5</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>จีรวรรณ มณีโชติ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ปลาวาฬ</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DRX-218</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>690122-1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>วิทวัส ศรีลำไย</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>โอริโอ้</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DRX-229</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>690127-1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>จัสติน</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DRX-236</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>690127-4</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>เบลล่า</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนรวม 6 โรค (วัคซีน,DW)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DRX-225</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>690126-1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>แชมป์</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>เท็ดดี้</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (สามารถฉีดวัคซีนรวม6โรคที่จะครบ 26/7/69 เลยก็ได้)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DRX-231</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>690127-2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>โทมัส</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DRX-235</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>690127-3</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>แพททริค</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DRX-239</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>690127-5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>วิลเลี่ยม</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
         </is>
       </c>
     </row>
@@ -794,7 +5353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -897,6 +5456,1951 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>690115-1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>แอฟ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>นมเย็น</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>690116-1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>รมณา</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ข้าวจ้าว</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>690117-1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>จุฑาทิพย์ เสลาหอม</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>มูมู่ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>690117-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>จุฑาทิพย์ เสลาหอม</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>มูมู่ (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (รวมแมว (2/3) + พิษสุนัขบ้า (1/2))</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>จรัสศรี จันทพย์วงษ์</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ไซเรน</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจแผล</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>690260-1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>อร</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ต้าว</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>690116-1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>รมณา</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ข้าวจ้าว</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>พัชราภรณ์ เอกเผ่าพันธุ์</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ทิกเกอร์</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า ( พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>690262-1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>นาตยา โพธิ์ม่วง</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>หมา</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>690120-1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>จำเนียร เศรษฐบุตร</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>แซลม่อน</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>690122-1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>วิทวัส ศรีลำไย</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>โอริโอ้</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>690212-1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ชรารินทร์ ลิ้มชัยโรจน์</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>แดง</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตัดไหม (ถอดแม็ก)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>690241-1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>สุทธินันท์ มุสิกาวัน</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ชีต้า</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (หูอักเสบ)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>690233-1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ชันสิทธ์ แช่มมินดา</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>690260-1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>อร</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ต้าว</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ฉีดยา</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>690123-1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>บี</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ญาญ่า</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนรวม 5 โรค (5 โรค (2/2))</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>พัชราภรณ์ เอกเผ่าพันธุ์</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ทิกเกอร์</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ฉี่เป็นมูกๆ)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>690213-1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ชนิดา ตระการนิธิ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>บะหมี่</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจเลือด (recheck CBC)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>690127-5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>วิลเลี่ยม</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP,สอบถามเพิ่มด้วยว่าวัคซีนครบเมื่อรัย)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>690127-1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>จัสติน</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>690245-1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>พิสิทธิ์    พนารัตนะโสรพ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ฮันเตอร์</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (recheck CCV/CPV test kit)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>690127-2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>โทมัส</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>690127-3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>แพททริค</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>690127-4</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>เบลล่า</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>690127-6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>เจนจิรา</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>เมมโมรี่</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (NGSP)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>690027-1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>นิภารัตน์ บัวพรม</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ไข่เจียว (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>690274-1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>บุหลัน สิงขรรักษ์</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>690268-1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ณัฐพงษ์ ริ้วทองชุม</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>เจ้าสัว</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>690203-1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>กาญ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>อ้อน</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>690027-1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>นิภารัตน์ บัวพรม</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ไข่เจียว (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>690134-1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>กฤตยา พิศุทธิภัทรา</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>แดดดี</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>690136-1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ลูกนัท</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>มีอาร์</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>690136-1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ลูกนัท</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>มีอาร์</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (รวมแมว (2/2) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>690222-1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ปัทมิษฏ์ สุวรรณวัฒนะ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ชาบู</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ปรารถนา ไวปัญญา</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>เหมย (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (เชื้อรา)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>จรัสศรี จันทพย์วงษ์</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ไซเรน</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตัดไหม</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>690102-1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ปัญญา  เหล็กดี</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>กุชชี่</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการท้องเสีย</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>กาแฟ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>กาแฟ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนลิวคิเมียแมว (ลิวคีเมีย (1/2) + test FeLV)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>690257-1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>สุณิสา</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>โชคดี</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจเลือด (cbc+ chem5)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>test_register_user</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>690217-1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>สงวน อินทร์รักษ์</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ชาบู</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>จ่ายยา — **รับยาพยาธิในเม็ดเลือดต่อเนื่อง</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>690131-1</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>อธิวรรณ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>นมสด</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>690200-1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>คุณสมชาย ทดสอบ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ขนมปัง</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>หมอนารีรัตน์</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ตรวจวัคซีน</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -919,7 +7423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -994,6 +7498,30 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:11:52</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sync</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DRX:97 → Queue+43</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/appointments.xlsx
+++ b/appointments.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:34</t>
+          <t>2026-05-26 20:37:54</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:35</t>
+          <t>2026-05-26 20:37:54</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:36</t>
+          <t>2026-05-26 20:37:55</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>690287-3</t>
+          <t>690287-2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ขายดี</t>
+          <t>ก๋วยเตี๋ยว</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:37</t>
+          <t>2026-05-26 20:37:56</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:38</t>
+          <t>2026-05-26 20:37:57</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:39</t>
+          <t>2026-05-26 20:37:58</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:40</t>
+          <t>2026-05-26 20:37:59</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:41</t>
+          <t>2026-05-26 20:38:00</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:42</t>
+          <t>2026-05-26 20:38:00</t>
         </is>
       </c>
     </row>
@@ -906,6 +906,425 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ub741455c24a2afcee792ea9d8af87077</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>พัชราภรณ์ เอกเผ่าพันธุ์</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ทิกเกอร์</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:34</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>690160-2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ธนากร เจริญธนารัตน์</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>พัมกิ้น</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:35</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>U7cc0f7ce8f6e545e67c7e77aa35db9ce</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>690289-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>นัฒริยา เลี้ยงอำนวย</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>แมวส้ม</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:36</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ณัฐวิญญ์ สิรเดชธราทิพย์</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>บราวนี่</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:37</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>690084-2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>แนน</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>มันนี่</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:38</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>U5d220d047421251dbe36331d61631e3a</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>690189-1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>นวรัตน์ พันเหนือ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>เฉาก๊วย</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:39</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>U835cf6a27aa276bd81a80630f363998b</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ปรารถนา ไวปัญญา</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>เหมย (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:40</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>U12d49c2dfd70e222ff4d4e5febe9a27a</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>690287-3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>กิ่งกมล เรืองหิรัญ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ขายดี</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0659561244</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:15</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>690160-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ธนากร เจริญธนารัตน์</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>โพเนีย</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0954486615</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:16</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:16</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>690299-3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ณัฐวิญญ์ สิรเดชธราทิพย์</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ส้มจิ๋ว</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:17</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:17</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>690299-2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ณัฐวิญญ์ สิรเดชธราทิพย์</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ฟ้าใส</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:18</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:18</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>690084-1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>แนน</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>เรนนี่</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:19</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>auto_sibling</t>
         </is>
@@ -922,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -997,37 +1416,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRX-524</t>
+          <t>DRX-577</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>690187-1</t>
+          <t>690276-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ธนัชญา แซ่มี</t>
+          <t>หญิง</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ปีเตอร์</t>
+          <t>วอดก้า</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบถามอาการ</t>
+          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1037,44 +1456,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRX-276</t>
+          <t>DRX-613</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>690144-1</t>
+          <t>690001-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ธนพล แทนประชา</t>
+          <t>Tarn Tarn.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ตัวเล็ก</t>
+          <t>หมูกะทะ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — Ultrasound (ตรวจท้อง)</t>
+          <t>ตรวจทั่วไป — ดูอาการ (โทร)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1084,14 +1503,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRX-597</t>
+          <t>DRX-615</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1116,12 +1535,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — อื่นๆ (Ngsp,โทร)</t>
+          <t>ตรวจทั่วไป — อื่นๆ (Ngsp)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1131,29 +1550,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRX-604</t>
+          <t>DRX-538</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690239-1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>นิลภวิษย์ ทับทอง</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>ฟ้า</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1163,12 +1582,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray (Ngsp)</t>
+          <t>ฉีดวัคซีน — วัคซีนไข้หัดและหวัดแมว (วัคซีน,ถ่ายพยาธิ,หยดยา,ดูอาการขา)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1178,44 +1597,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRX-605</t>
+          <t>DRX-560</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>690280-1</t>
+          <t>690001-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>คณิติน ยวนแหล</t>
+          <t>Tarn Tarn.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>จิ๋ว</t>
+          <t>หมูกะทะ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ทำแผล</t>
+          <t>ตรวจทั่วไป — ให้น้ำเกลือ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1225,44 +1644,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DRX-578</t>
+          <t>DRX-585</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>690263-1</t>
+          <t>690224-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>จันทร์รวี</t>
+          <t>มัลลิณี ศรีจันทร์</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>แตงกวา</t>
+          <t>คิรัว</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ</t>
+          <t>ตรวจทั่วไป — X-ray</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1272,29 +1691,29 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DRX-584</t>
+          <t>DRX-612</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690001-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>Tarn Tarn.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>หมูกะทะ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1304,12 +1723,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ฉีดยา</t>
+          <t>ตรวจทั่วไป — X-ray</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1319,44 +1738,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DRX-593</t>
+          <t>DRX-614</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>690245-1</t>
+          <t>690001-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>พิสิทธิ์    พนารัตนะโสรพ</t>
+          <t>Tarn Tarn.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ฮันเตอร์</t>
+          <t>หมูกะทะ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>มัลลินี</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว</t>
+          <t>ตรวจทั่วไป — ดูอาการ (โทรถาม)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1366,44 +1785,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRX-603</t>
+          <t>DRX-641</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690296-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>รต ไพศาล อิศรางกูร</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>เจี๊ยบ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — อื่นๆ (Ivm)</t>
+          <t>ตรวจทั่วไป — โทรสอบถามเรื่องคลอด</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1413,29 +1832,29 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRX-619</t>
+          <t>DRX-300</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>690289-1</t>
+          <t>690162-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>นัฒริยา เลี้ยงอำนวย</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>แมวส้ม</t>
+          <t>ชาเย็น</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1445,12 +1864,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1460,44 +1879,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DRX-537</t>
+          <t>DRX-301</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690274-1</t>
+          <t>690162-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>บุหลัน สิงขรรักษ์</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>มันนี่</t>
+          <t>ชาเย็น</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ตัดไหม</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1507,29 +1926,29 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DRX-577</t>
+          <t>DRX-561</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>690276-1</t>
+          <t>690277-1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>หญิง</t>
+          <t>อภิญญา สุขใจ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>วอดก้า</t>
+          <t>อวกาศ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1539,12 +1958,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
+          <t>ตรวจทั่วไป — ดูอาการ,ตรวจเลือด (cbc)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1554,44 +1973,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DRX-613</t>
+          <t>DRX-309</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690007-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>สุชาวดี ชาติกานนท์</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>มันนี่</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทร)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1601,44 +2020,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DRX-615</t>
+          <t>DRX-647</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690289-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>นัฒริยา เลี้ยงอำนวย</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>แมวส้ม</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — อื่นๆ (Ngsp)</t>
+          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1648,29 +2067,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRX-616</t>
+          <t>DRX-295</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690257-1</t>
+          <t>690159-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>สุณิสา</t>
+          <t>พรพรรณ ณัฐวุฒิ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>โชคดี</t>
+          <t>หมูแดง</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1680,12 +2099,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ฉีดยา (ฉีด EPO)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1695,44 +2114,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DRX-538</t>
+          <t>DRX-299</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690239-1</t>
+          <t>690160-1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>นิลภวิษย์ ทับทอง</t>
+          <t>ธนากร เจริญธนารัตน์</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ฟ้า</t>
+          <t>โพเนีย</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>มัลลินี</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนไข้หัดและหวัดแมว (วัคซีน,ถ่ายพยาธิ,หยดยา,ดูอาการขา)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1742,44 +2161,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DRX-560</t>
+          <t>DRX-303</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690162-2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>สแกมเมอร์</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ให้น้ำเกลือ</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1789,44 +2208,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DRX-585</t>
+          <t>DRX-304</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690162-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>สแกมเมอร์</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2)+ พิษสุนัข (2/2))</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1836,44 +2255,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DRX-609</t>
+          <t>DRX-564</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>690201-1</t>
+          <t>690130-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ปรารถนา ไวปัญญา</t>
+          <t>กานดา ตันติสกุลเลิศ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>เหมย (แพคเกจวัคซีน)</t>
+          <t>คุมะ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ทำแผล (ฟอกเชื้อรา)</t>
+          <t>ตรวจทั่วไป — รับยาต่อเนื่อง (โทรถามอาการ + รับยาต่อเนื่อง)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1883,44 +2302,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DRX-612</t>
+          <t>DRX-568</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690241-1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>สุทธินันท์ มุสิกาวัน</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>ชีต้า</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ตรวจทั่วไป — โทรถามอาการเรื่องคันหู</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1930,29 +2349,29 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DRX-614</t>
+          <t>DRX-586</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690224-1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>มัลลิณี ศรีจันทร์</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>คิรัว</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1962,12 +2381,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทรถาม)</t>
+          <t>ตรวจทั่วไป — Ultrasound</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1977,29 +2396,29 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DRX-620</t>
+          <t>DRX-617</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>690152-4</t>
+          <t>690291-1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ปวริศ มากสอน</t>
+          <t>ธนิตา ถวิลวิสา</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>บีน่า</t>
+          <t>จากัวร์</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2009,12 +2428,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (เท้าบวม)</t>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการถ่ายเหลว</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2024,29 +2443,29 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DRX-300</t>
+          <t>DRX-621</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>690162-1</t>
+          <t>690293-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สริตา ปรึกษากร</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ชาเย็น</t>
+          <t>มีเธอ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2056,7 +2475,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — โทรสอบอาการ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2071,44 +2490,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DRX-301</t>
+          <t>DRX-587</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>690162-1</t>
+          <t>690224-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>มัลลิณี ศรีจันทร์</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ชาเย็น</t>
+          <t>คิรัว</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — ตรวจเลือด</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2118,44 +2537,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DRX-561</t>
+          <t>DRX-645</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>690277-1</t>
+          <t>690257-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>อภิญญา สุขใจ</t>
+          <t>สุณิสา</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>อวกาศ</t>
+          <t>โชคดี</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,ตรวจเลือด (cbc)</t>
+          <t>ตรวจทั่วไป — ฉีดยา (ฉีด EPO)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2165,44 +2584,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DRX-309</t>
+          <t>DRX-592</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>690007-1</t>
+          <t>690278-1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>สุชาวดี ชาติกานนท์</t>
+          <t>สุทธิ เข้มกำเนิด</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>มันนี่</t>
+          <t>ทอง</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2212,44 +2631,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DRX-295</t>
+          <t>DRX-639</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>690159-1</t>
+          <t>690280-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>พรพรรณ ณัฐวุฒิ</t>
+          <t>คณิติน ยวนแหล</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>หมูแดง</t>
+          <t>จิ๋ว</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>เบญจมาศ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ทำแผล</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2259,44 +2678,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DRX-299</t>
+          <t>DRX-320</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>690160-1</t>
+          <t>690171-2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ธนากร เจริญธนารัตน์</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>โพเนีย</t>
+          <t>ไดม่อน</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>มัลลินี</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2306,29 +2725,29 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DRX-303</t>
+          <t>DRX-321</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>690162-2</t>
+          <t>690171-2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>สแกมเมอร์</t>
+          <t>ไดม่อน</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2338,12 +2757,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2353,29 +2772,29 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DRX-304</t>
+          <t>DRX-323</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>690162-2</t>
+          <t>690171-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>สแกมเมอร์</t>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2385,12 +2804,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2)+ พิษสุนัข (2/2))</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2400,44 +2819,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DRX-564</t>
+          <t>DRX-329</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>690130-1</t>
+          <t>690178-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>กานดา ตันติสกุลเลิศ</t>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>คุมะ</t>
+          <t>มะยม (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — รับยาต่อเนื่อง (โทรถามอาการ + รับยาต่อเนื่อง)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2447,44 +2866,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DRX-568</t>
+          <t>DRX-322</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>690241-1</t>
+          <t>690171-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>สุทธินันท์ มุสิกาวัน</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ชีต้า</t>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรถามอาการเรื่องคันหู</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2494,44 +2913,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DRX-586</t>
+          <t>DRX-328</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690178-1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>มะยม (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — Ultrasound</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2541,44 +2960,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DRX-617</t>
+          <t>DRX-589</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>690291-1</t>
+          <t>690284-1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ธนิตา ถวิลวิสา</t>
+          <t>จันทนี เซี่ยงคิ้ว</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>จากัวร์</t>
+          <t>ชานม</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบถามอาการถ่ายเหลว</t>
+          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2588,44 +3007,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DRX-621</t>
+          <t>DRX-600</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>690293-1</t>
+          <t>690136-1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>สริตา ปรึกษากร</t>
+          <t>ลูกนัท</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>มีเธอ</t>
+          <t>มีอาร์</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบอาการ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- กระตุ้นวัคซีน รวม2/2 + RV2/2)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2635,44 +3054,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DRX-587</t>
+          <t>DRX-638</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690295-1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>สุพรรษา วิโอประเสริฐ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>กะทิ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ตรวจเลือด</t>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการไอ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2682,44 +3101,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DRX-592</t>
+          <t>DRX-643</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>690278-1</t>
+          <t>690298-1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>สุทธิ เข้มกำเนิด</t>
+          <t>กรรณิการ์ วุฒิกุล</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ทอง</t>
+          <t>มาตังค์</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ตาบวม)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2729,29 +3148,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DRX-320</t>
+          <t>DRX-644</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>690171-2</t>
+          <t>690152-4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ปวริศ มากสอน</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ไดม่อน</t>
+          <t>บีน่า</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2761,7 +3180,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — ดูอาการ (เท้าบวม)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2776,29 +3195,29 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DRX-321</t>
+          <t>DRX-606</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>690171-2</t>
+          <t>690287-1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>กิ่งกมล เรืองหิรัญ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ไดม่อน</t>
+          <t>ไก่ตุ๋น</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2808,12 +3227,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ระบบประสาท)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2823,29 +3242,29 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DRX-323</t>
+          <t>DRX-651</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>690171-1</t>
+          <t>690201-1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ปรารถนา ไวปัญญา</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+          <t>เหมย (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2855,12 +3274,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ฟอกเชื้อรา + รับยาต่อเนื่อง)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2870,29 +3289,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DRX-329</t>
+          <t>DRX-602</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>690178-1</t>
+          <t>690206-2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+          <t>สุฐิษา ธนาการกิตติสุข</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>มะยม (แพคเกจวัคซีน)</t>
+          <t>นีออน</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2902,12 +3321,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (โทรสอบถามอาการ)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2917,29 +3336,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DRX-322</t>
+          <t>DRX-618</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>690171-1</t>
+          <t>690291-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ธนิตา ถวิลวิสา</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+          <t>จากัวร์</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2949,12 +3368,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- ทำวัคซีนเข็มแรก)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2964,29 +3383,29 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DRX-328</t>
+          <t>DRX-622</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>690178-1</t>
+          <t>690293-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+          <t>สริตา ปรึกษากร</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>มะยม (แพคเกจวัคซีน)</t>
+          <t>มีเธอ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2996,12 +3415,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- วัคซีนเข็มแรก)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3011,44 +3430,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DRX-589</t>
+          <t>DRX-516</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>690284-1</t>
+          <t>690092-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>จันทนี เซี่ยงคิ้ว</t>
+          <t>ธนภรณ์</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ชานม</t>
+          <t>ทองมา</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>มัลลินี</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3058,44 +3477,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DRX-600</t>
+          <t>DRX-357</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>690136-1</t>
+          <t>690196-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ลูกนัท</t>
+          <t>อนัญญา เทียนธนะวัฒธ์</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>มีอาร์</t>
+          <t>ฮันนี่</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- กระตุ้นวัคซีน รวม2/2 + RV2/2)</t>
+          <t>ตรวจทั่วไป — X-ray</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3105,29 +3524,29 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DRX-606</t>
+          <t>DRX-64</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>690287-1</t>
+          <t>690038-2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>กิ่งกมล เรืองหิรัญ</t>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ไก่ตุ๋น</t>
+          <t>ขุมทรัพย์</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3137,12 +3556,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ระบบประสาท)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3152,29 +3571,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DRX-602</t>
+          <t>DRX-65</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>690206-2</t>
+          <t>690038-1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>สุฐิษา ธนาการกิตติสุข</t>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>นีออน</t>
+          <t>โยดา</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3184,12 +3603,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทรสอบถามอาการ)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3199,44 +3618,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DRX-618</t>
+          <t>DRX-69</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>690291-1</t>
+          <t>690043-1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ธนิตา ถวิลวิสา</t>
+          <t>รื่นรมย์ เหรียญทอง</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>จากัวร์</t>
+          <t>สองสี</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- ทำวัคซีนเข็มแรก)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3246,44 +3665,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DRX-622</t>
+          <t>DRX-81</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>690293-1</t>
+          <t>690039-1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>สริตา ปรึกษากร</t>
+          <t>อาร์ม</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>มีเธอ</t>
+          <t>สาคู</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- วัคซีนเข็มแรก)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3293,44 +3712,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DRX-516</t>
+          <t>DRX-85</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>690092-1</t>
+          <t>690026-2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ธนภรณ์</t>
+          <t>ญานิศา แรงจันทร์</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ทองมา</t>
+          <t>ชิโร่ (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>มัลลินี</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3340,44 +3759,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DRX-357</t>
+          <t>DRX-87</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>690196-1</t>
+          <t>690056-1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>อนัญญา เทียนธนะวัฒธ์</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ฮันนี่</t>
+          <t>ไอโชค</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (BVT,DW)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3387,29 +3806,29 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DRX-64</t>
+          <t>DRX-110</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>690038-2</t>
+          <t>690067-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+          <t>ไก่</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ขุมทรัพย์</t>
+          <t>อั่งเปา</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3419,12 +3838,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3434,29 +3853,29 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DRX-65</t>
+          <t>DRX-117</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>690038-1</t>
+          <t>690072-1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+          <t>ปิ่นแก้ว</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>โยดา</t>
+          <t>มาโร</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3471,7 +3890,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3481,44 +3900,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DRX-69</t>
+          <t>DRX-126</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>690043-1</t>
+          <t>690076-1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>รื่นรมย์ เหรียญทอง</t>
+          <t>อรพรรณ  ขำสุวรรณ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>สองสี</t>
+          <t>น้องถุงเงิน</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3528,44 +3947,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DRX-81</t>
+          <t>DRX-142</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>690039-1</t>
+          <t>690082-1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>อาร์ม</t>
+          <t>ประชุม คุณท้าวเทียม</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>สาคู</t>
+          <t>มีบุญ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3575,29 +3994,29 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DRX-85</t>
+          <t>DRX-151</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>690026-2</t>
+          <t>690096-1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ญานิศา แรงจันทร์</t>
+          <t>กฤตยา วิเชียรพาย</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ชิโร่ (แพคเกจวัคซีน)</t>
+          <t>ซาร่า</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3607,12 +4026,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3622,44 +4041,44 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DRX-87</t>
+          <t>DRX-161</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>690056-1</t>
+          <t>690100-1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>พิสิทธิ์    สามกองงาม</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ไอโชค</t>
+          <t>กิมจิ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (BVT,DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3669,29 +4088,29 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DRX-110</t>
+          <t>DRX-159</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>690067-1</t>
+          <t>690100-2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ไก่</t>
+          <t>พิสิทธิ์    สามกองงาม</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>อั่งเปา</t>
+          <t>โซจู</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3701,12 +4120,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3716,29 +4135,29 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DRX-117</t>
+          <t>DRX-163</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>690072-1</t>
+          <t>690056-2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ปิ่นแก้ว</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>มาโร</t>
+          <t>เฉาก๊วย</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3748,12 +4167,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3763,29 +4182,29 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DRX-126</t>
+          <t>DRX-164</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>690076-1</t>
+          <t>690056-3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>อรพรรณ  ขำสุวรรณ</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>น้องถุงเงิน</t>
+          <t>พาดกลอน</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3800,7 +4219,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3810,29 +4229,29 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DRX-142</t>
+          <t>DRX-174</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>690082-1</t>
+          <t>690056-4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ประชุม คุณท้าวเทียม</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>มีบุญ</t>
+          <t>บี1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3842,12 +4261,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3857,29 +4276,29 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DRX-151</t>
+          <t>DRX-180</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>690096-1</t>
+          <t>690042-2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>กฤตยา วิเชียรพาย</t>
+          <t>วราฤทธิ์ บัวโต</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ซาร่า</t>
+          <t>ดั๊ก</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3889,12 +4308,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3904,29 +4323,29 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DRX-161</t>
+          <t>DRX-172</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>690100-1</t>
+          <t>690056-5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>พิสิทธิ์    สามกองงาม</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>กิมจิ</t>
+          <t>บี2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3936,12 +4355,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3951,29 +4370,29 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DRX-159</t>
+          <t>DRX-191</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>690100-2</t>
+          <t>690009-6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>พิสิทธิ์    สามกองงาม</t>
+          <t>ธนาวดี เมธา</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>โซจู</t>
+          <t>ปลาหมึก</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3988,7 +4407,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3998,29 +4417,29 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DRX-163</t>
+          <t>DRX-210</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>690056-2</t>
+          <t>690064-2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>เฉาก๊วย</t>
+          <t>พลูโต</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4035,7 +4454,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4045,29 +4464,29 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DRX-164</t>
+          <t>DRX-211</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>690056-3</t>
+          <t>690064-3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>พาดกลอน</t>
+          <t>ชาแนล</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4082,7 +4501,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4092,29 +4511,29 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DRX-174</t>
+          <t>DRX-212</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>690056-4</t>
+          <t>690064-4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>บี1</t>
+          <t>เนปจูน</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4129,7 +4548,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4139,54 +4558,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-05-25 18:39:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>DRX-180</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>690042-2</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>วราฤทธิ์ บัวโต</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ดั๊ก</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-05-25 18:39:27</t>
+          <t>2026-05-26 20:36:12</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6077,7 +6449,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -6177,7 +6549,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -6277,7 +6649,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -7196,6 +7568,196 @@
         </is>
       </c>
       <c r="P59" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>10033</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>690224-1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>มัลลิณี ศรีจันทร์</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>คิรัว</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ตรวจเลือด</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>U319ce6867f8c2e421e72170330fca9ce</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:00:02</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>10034</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>690278-1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>สุทธิ เข้มกำเนิด</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ทอง</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>สัตวแพทย์</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>10035</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>690280-1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>คณิติน ยวนแหล</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>จิ๋ว</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>เบญจมาศ</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ทำแผล</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>10036</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>690257-1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>สุณิสา</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>โชคดี</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ฉีดยา (ฉีด EPO)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>drx</t>
         </is>
@@ -7223,7 +7785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10080,6 +10642,1546 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-25 20:15:14</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DRX:66</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:30:18</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DRX:71</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:00:02</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Queue_Build</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Queue+3</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:15:15</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>DRX:68</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:24</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>DRX:67</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Ud4b955ac4ddd56e12f2ab3cbc77f790b</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Ub52a3ad9704e3f5c3194c5cf96875084</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:27</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>690224-1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>U319ce6867f8c2e421e72170330fca9ce</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:28</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>690287-2</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>U12d49c2dfd70e222ff4d4e5febe9a27a</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:29</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>U767d6bba954a02bc3bd47fa2156cefb2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>690284-1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Ue95e6b9adfedfe87453d8d88c805be9a</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:31</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>690291-1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>U85ffc0c0ed720e5aa118f80fe81e4f51</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:32</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Ud3199338d71e5f310af197255682ff41</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:33</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>690157-1</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>U9d5f25862cbd9d2fe2c58bb5ba7c532f</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:34</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Ub741455c24a2afcee792ea9d8af87077</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:35</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>690160-2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:36</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>690289-1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>U7cc0f7ce8f6e545e67c7e77aa35db9ce</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>690084-2</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>690189-1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>U5d220d047421251dbe36331d61631e3a</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:40</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>U835cf6a27aa276bd81a80630f363998b</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>new customer (1/2)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:36:42</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Queue_Build</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Queue+1</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:54</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Ud4b955ac4ddd56e12f2ab3cbc77f790b</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:54</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ub52a3ad9704e3f5c3194c5cf96875084</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:55</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>690224-1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>U319ce6867f8c2e421e72170330fca9ce</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:56</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>690287-2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>U12d49c2dfd70e222ff4d4e5febe9a27a</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:57</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>U767d6bba954a02bc3bd47fa2156cefb2</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:58</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>690284-1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ue95e6b9adfedfe87453d8d88c805be9a</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:37:59</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>690291-1</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>U85ffc0c0ed720e5aa118f80fe81e4f51</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Ud3199338d71e5f310af197255682ff41</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:01</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>690157-1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>U9d5f25862cbd9d2fe2c58bb5ba7c532f</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Ub741455c24a2afcee792ea9d8af87077</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:02</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>690160-2</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>690289-1</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>U7cc0f7ce8f6e545e67c7e77aa35db9ce</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:04</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:05</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>690084-2</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:06</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>690189-1</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>U5d220d047421251dbe36331d61631e3a</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:38:07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>U835cf6a27aa276bd81a80630f363998b</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:09</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ub741455c24a2afcee792ea9d8af87077</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:10</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>690160-2</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>690289-1</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>U7cc0f7ce8f6e545e67c7e77aa35db9ce</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>690084-2</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>690189-1</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>U5d220d047421251dbe36331d61631e3a</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:14</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>U835cf6a27aa276bd81a80630f363998b</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>690287-3</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>U12d49c2dfd70e222ff4d4e5febe9a27a</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>sibling HN → ขายดี</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:16</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>690160-1</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>sibling HN → โพเนีย</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:17</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>690299-3</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>sibling HN → ส้มจิ๋ว</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:18</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>690299-2</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>sibling HN → ฟ้าใส</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-26 20:40:19</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>690084-1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>sibling HN → เรนนี่</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/appointments.xlsx
+++ b/appointments.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:54</t>
+          <t>2026-05-26 21:05:09</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:54</t>
+          <t>2026-05-26 21:05:10</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:55</t>
+          <t>2026-05-26 21:05:11</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:56</t>
+          <t>2026-05-26 21:05:12</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:57</t>
+          <t>2026-05-26 21:05:13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:58</t>
+          <t>2026-05-26 21:05:14</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-26 20:37:59</t>
+          <t>2026-05-26 21:05:15</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-05-26 20:38:00</t>
+          <t>2026-05-26 21:05:15</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-05-26 20:38:00</t>
+          <t>2026-05-26 21:05:16</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:08</t>
+          <t>2026-05-26 21:05:17</t>
         </is>
       </c>
     </row>
@@ -964,6 +964,9 @@
           <t>พัมกิ้น</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>954486615</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-05-26 20:36:35</t>
@@ -971,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:09</t>
+          <t>2026-05-26 21:05:18</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1006,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:10</t>
+          <t>2026-05-26 21:05:19</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1018,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690299-1</t>
+          <t>690299-3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1025,7 +1028,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>บราวนี่</t>
+          <t>ส้มจิ๋ว</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1035,7 +1038,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:11</t>
+          <t>2026-05-26 21:05:20</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1070,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:12</t>
+          <t>2026-05-26 21:05:21</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1102,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:13</t>
+          <t>2026-05-26 21:05:22</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1134,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-26 20:40:14</t>
+          <t>2026-05-26 21:05:23</t>
         </is>
       </c>
     </row>
@@ -1325,6 +1328,85 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ณัฐวิญญ์ สิรเดชธราทิพย์</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>บราวนี่</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:30:15</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:30:15</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>auto_sibling</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>690084-3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>แนน</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ชาไทย</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0660146423</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-27 20:15:12</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-05-27 20:15:12</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>auto_sibling</t>
         </is>
@@ -1341,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1416,37 +1498,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRX-577</t>
+          <t>DRX-300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>690276-1</t>
+          <t>690162-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>หญิง</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>วอดก้า</t>
+          <t>ชาเย็น</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1456,44 +1538,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRX-613</t>
+          <t>DRX-301</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690162-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>ชาเย็น</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทร)</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1503,44 +1585,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRX-615</t>
+          <t>DRX-309</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690007-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>สุชาวดี ชาติกานนท์</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>มันนี่</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — อื่นๆ (Ngsp)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1550,44 +1632,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRX-538</t>
+          <t>DRX-295</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>690239-1</t>
+          <t>690159-1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>นิลภวิษย์ ทับทอง</t>
+          <t>พรพรรณ ณัฐวุฒิ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ฟ้า</t>
+          <t>หมูแดง</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนไข้หัดและหวัดแมว (วัคซีน,ถ่ายพยาธิ,หยดยา,ดูอาการขา)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1597,44 +1679,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRX-560</t>
+          <t>DRX-303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690162-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>สแกมเมอร์</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ให้น้ำเกลือ</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1644,44 +1726,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DRX-585</t>
+          <t>DRX-304</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690162-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>นุชอนงค์ กุลกิตติโกวิท</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>สแกมเมอร์</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2)+ พิษสุนัข (2/2))</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1691,44 +1773,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DRX-612</t>
+          <t>DRX-568</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690241-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>สุทธินันท์ มุสิกาวัน</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>ชีต้า</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ตรวจทั่วไป — โทรถามอาการเรื่องคันหู</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1738,29 +1820,29 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DRX-614</t>
+          <t>DRX-586</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>690001-1</t>
+          <t>690224-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarn Tarn.</t>
+          <t>มัลลิณี ศรีจันทร์</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>หมูกะทะ</t>
+          <t>คิรัว</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1770,12 +1852,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทรถาม)</t>
+          <t>ตรวจทั่วไป — Ultrasound</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1785,29 +1867,29 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DRX-641</t>
+          <t>DRX-617</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>690296-1</t>
+          <t>690291-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>รต ไพศาล อิศรางกูร</t>
+          <t>ธนิตา ถวิลวิสา</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>เจี๊ยบ</t>
+          <t>จากัวร์</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1817,12 +1899,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบถามเรื่องคลอด</t>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการถ่ายเหลว</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1832,29 +1914,29 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DRX-300</t>
+          <t>DRX-621</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>690162-1</t>
+          <t>690293-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สริตา ปรึกษากร</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ชาเย็น</t>
+          <t>มีเธอ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1864,7 +1946,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — โทรสอบอาการ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1879,44 +1961,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DRX-301</t>
+          <t>DRX-587</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>690162-1</t>
+          <t>690224-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>มัลลิณี ศรีจันทร์</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ชาเย็น</t>
+          <t>คิรัว</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — ตรวจเลือด</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1926,44 +2008,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DRX-561</t>
+          <t>DRX-645</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>690277-1</t>
+          <t>690257-1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>อภิญญา สุขใจ</t>
+          <t>สุณิสา</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>อวกาศ</t>
+          <t>โชคดี</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,ตรวจเลือด (cbc)</t>
+          <t>ตรวจทั่วไป — ฉีดยา (ฉีด EPO)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1973,44 +2055,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DRX-309</t>
+          <t>DRX-592</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>690007-1</t>
+          <t>690278-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>สุชาวดี ชาติกานนท์</t>
+          <t>สุทธิ เข้มกำเนิด</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>มันนี่</t>
+          <t>ทอง</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2020,44 +2102,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DRX-647</t>
+          <t>DRX-639</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>690289-1</t>
+          <t>690280-1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>นัฒริยา เลี้ยงอำนวย</t>
+          <t>คณิติน ยวนแหล</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>แมวส้ม</t>
+          <t>จิ๋ว</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>เบญจมาศ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
+          <t>ตรวจทั่วไป — ทำแผล</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2067,29 +2149,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRX-295</t>
+          <t>DRX-663</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690159-1</t>
+          <t>690289-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>พรพรรณ ณัฐวุฒิ</t>
+          <t>นัฒริยา เลี้ยงอำนวย</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>หมูแดง</t>
+          <t>แมวส้ม</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2099,12 +2181,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ทำแผล,ฉีดยา</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2114,44 +2196,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DRX-299</t>
+          <t>DRX-320</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>690160-1</t>
+          <t>690171-2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ธนากร เจริญธนารัตน์</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>โพเนีย</t>
+          <t>ไดม่อน</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>มัลลินี</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2161,29 +2243,29 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DRX-303</t>
+          <t>DRX-321</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>690162-2</t>
+          <t>690171-2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>สแกมเมอร์</t>
+          <t>ไดม่อน</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2193,12 +2275,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2208,29 +2290,29 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DRX-304</t>
+          <t>DRX-323</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>690162-2</t>
+          <t>690171-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>นุชอนงค์ กุลกิตติโกวิท</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>สแกมเมอร์</t>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2240,12 +2322,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/2)+ พิษสุนัข (2/2))</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2255,44 +2337,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DRX-564</t>
+          <t>DRX-329</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>690130-1</t>
+          <t>690178-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>กานดา ตันติสกุลเลิศ</t>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>คุมะ</t>
+          <t>มะยม (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — รับยาต่อเนื่อง (โทรถามอาการ + รับยาต่อเนื่อง)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2302,44 +2384,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DRX-568</t>
+          <t>DRX-322</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>690241-1</t>
+          <t>690171-1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>สุทธินันท์ มุสิกาวัน</t>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ชีต้า</t>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรถามอาการเรื่องคันหู</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2349,44 +2431,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DRX-586</t>
+          <t>DRX-328</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690178-1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>มะยม (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — Ultrasound</t>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2396,44 +2478,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DRX-617</t>
+          <t>DRX-589</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>690291-1</t>
+          <t>690284-1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ธนิตา ถวิลวิสา</t>
+          <t>จันทนี เซี่ยงคิ้ว</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>จากัวร์</t>
+          <t>ชานม</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบถามอาการถ่ายเหลว</t>
+          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2443,44 +2525,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DRX-621</t>
+          <t>DRX-600</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>690293-1</t>
+          <t>690136-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>สริตา ปรึกษากร</t>
+          <t>ลูกนัท</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>มีเธอ</t>
+          <t>มีอาร์</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>สัตวแพทย์</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบอาการ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- กระตุ้นวัคซีน รวม2/2 + RV2/2)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2490,44 +2572,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DRX-587</t>
+          <t>DRX-638</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>690224-1</t>
+          <t>690295-1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>มัลลิณี ศรีจันทร์</t>
+          <t>สุพรรษา วิโอประเสริฐ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>คิรัว</t>
+          <t>กะทิ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ตรวจเลือด</t>
+          <t>ตรวจทั่วไป — โทรสอบถามอาการไอ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2537,29 +2619,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DRX-645</t>
+          <t>DRX-643</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>690257-1</t>
+          <t>690298-1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>สุณิสา</t>
+          <t>กรรณิการ์ วุฒิกุล</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>โชคดี</t>
+          <t>มาตังค์</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2569,12 +2651,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ฉีดยา (ฉีด EPO)</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ตาบวม)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2584,44 +2666,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DRX-592</t>
+          <t>DRX-644</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>690278-1</t>
+          <t>690152-4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>สุทธิ เข้มกำเนิด</t>
+          <t>ปวริศ มากสอน</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ทอง</t>
+          <t>บีน่า</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (เท้าบวม)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2631,44 +2713,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DRX-639</t>
+          <t>DRX-606</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>690280-1</t>
+          <t>690287-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>คณิติน ยวนแหล</t>
+          <t>กิ่งกมล เรืองหิรัญ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>จิ๋ว</t>
+          <t>ไก่ตุ๋น</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>เบญจมาศ</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ทำแผล</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ระบบประสาท)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2678,29 +2760,29 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DRX-320</t>
+          <t>DRX-651</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>690171-2</t>
+          <t>690201-1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ปรารถนา ไวปัญญา</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ไดม่อน</t>
+          <t>เหมย (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2710,12 +2792,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ฟอกเชื้อรา + รับยาต่อเนื่อง)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2725,29 +2807,29 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DRX-321</t>
+          <t>DRX-602</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>690171-2</t>
+          <t>690206-2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>สุฐิษา ธนาการกิตติสุข</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ไดม่อน</t>
+          <t>นีออน</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2757,12 +2839,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ (โทรสอบถามอาการ)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2772,29 +2854,29 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DRX-323</t>
+          <t>DRX-618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>690171-1</t>
+          <t>690291-1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ธนิตา ถวิลวิสา</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+          <t>จากัวร์</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2804,12 +2886,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- ทำวัคซีนเข็มแรก)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2819,29 +2901,29 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DRX-329</t>
+          <t>DRX-622</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>690178-1</t>
+          <t>690293-1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+          <t>สริตา ปรึกษากร</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>มะยม (แพคเกจวัคซีน)</t>
+          <t>มีเธอ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2851,12 +2933,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- วัคซีนเข็มแรก)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2866,44 +2948,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DRX-322</t>
+          <t>DRX-516</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>690171-1</t>
+          <t>690092-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>สุดารัตน์ โพธิ์ทอง</t>
+          <t>ธนภรณ์</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+          <t>ทองมา</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>มัลลินี</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
+          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2913,29 +2995,29 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DRX-328</t>
+          <t>DRX-357</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>690178-1</t>
+          <t>690196-1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+          <t>อนัญญา เทียนธนะวัฒธ์</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>มะยม (แพคเกจวัคซีน)</t>
+          <t>ฮันนี่</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2945,12 +3027,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
+          <t>ตรวจทั่วไป — X-ray</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2960,44 +3042,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DRX-589</t>
+          <t>DRX-664</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>690284-1</t>
+          <t>690302-1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>จันทนี เซี่ยงคิ้ว</t>
+          <t>ธัญสินี กาญจนสิทธิ์</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ชานม</t>
+          <t>คาฟู</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
+          <t>ตรวจทั่วไป — ตัดไหม</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3007,44 +3089,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DRX-600</t>
+          <t>DRX-64</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>690136-1</t>
+          <t>690038-2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ลูกนัท</t>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>มีอาร์</t>
+          <t>ขุมทรัพย์</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>สัตวแพทย์</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- กระตุ้นวัคซีน รวม2/2 + RV2/2)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3054,29 +3136,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DRX-638</t>
+          <t>DRX-65</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>690295-1</t>
+          <t>690038-1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>สุพรรษา วิโอประเสริฐ</t>
+          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>กะทิ</t>
+          <t>โยดา</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3086,12 +3168,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — โทรสอบถามอาการไอ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3101,44 +3183,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DRX-643</t>
+          <t>DRX-69</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>690298-1</t>
+          <t>690043-1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>กรรณิการ์ วุฒิกุล</t>
+          <t>รื่นรมย์ เหรียญทอง</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>มาตังค์</t>
+          <t>สองสี</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ตาบวม)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3148,44 +3230,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DRX-644</t>
+          <t>DRX-81</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>690152-4</t>
+          <t>690039-1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ปวริศ มากสอน</t>
+          <t>อาร์ม</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>บีน่า</t>
+          <t>สาคู</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (เท้าบวม)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3195,29 +3277,29 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DRX-606</t>
+          <t>DRX-85</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>690287-1</t>
+          <t>690026-2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>กิ่งกมล เรืองหิรัญ</t>
+          <t>ญานิศา แรงจันทร์</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ไก่ตุ๋น</t>
+          <t>ชิโร่ (แพคเกจวัคซีน)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3227,12 +3309,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ระบบประสาท)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3242,44 +3324,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DRX-651</t>
+          <t>DRX-87</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>690201-1</t>
+          <t>690056-1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ปรารถนา ไวปัญญา</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>เหมย (แพคเกจวัคซีน)</t>
+          <t>ไอโชค</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ฟอกเชื้อรา + รับยาต่อเนื่อง)</t>
+          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (BVT,DW)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3289,29 +3371,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DRX-602</t>
+          <t>DRX-110</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>690206-2</t>
+          <t>690067-1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>สุฐิษา ธนาการกิตติสุข</t>
+          <t>ไก่</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>นีออน</t>
+          <t>อั่งเปา</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3321,12 +3403,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (โทรสอบถามอาการ)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3336,29 +3418,29 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DRX-618</t>
+          <t>DRX-117</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>690291-1</t>
+          <t>690072-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ธนิตา ถวิลวิสา</t>
+          <t>ปิ่นแก้ว</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>จากัวร์</t>
+          <t>มาโร</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3368,12 +3450,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- ทำวัคซีนเข็มแรก)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3383,29 +3465,29 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DRX-622</t>
+          <t>DRX-126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>690293-1</t>
+          <t>690076-1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>สริตา ปรึกษากร</t>
+          <t>อรพรรณ  ขำสุวรรณ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>มีเธอ</t>
+          <t>น้องถุงเงิน</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3415,12 +3497,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (+/- วัคซีนเข็มแรก)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3430,44 +3512,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DRX-516</t>
+          <t>DRX-142</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>690092-1</t>
+          <t>690082-1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ธนภรณ์</t>
+          <t>ประชุม คุณท้าวเทียม</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ทองมา</t>
+          <t>มีบุญ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>มัลลินี</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ดูอาการ (ตรวจตา)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3477,29 +3559,29 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DRX-357</t>
+          <t>DRX-151</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>690196-1</t>
+          <t>690096-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>อนัญญา เทียนธนะวัฒธ์</t>
+          <t>กฤตยา วิเชียรพาย</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ฮันนี่</t>
+          <t>ซาร่า</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3509,12 +3591,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — X-ray</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3524,29 +3606,29 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DRX-64</t>
+          <t>DRX-161</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>690038-2</t>
+          <t>690100-1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+          <t>พิสิทธิ์    สามกองงาม</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ขุมทรัพย์</t>
+          <t>กิมจิ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3561,7 +3643,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3571,29 +3653,29 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DRX-65</t>
+          <t>DRX-159</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>690038-1</t>
+          <t>690100-2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>วริทธ์นานนท์ ขจิตศาตนันท์</t>
+          <t>พิสิทธิ์    สามกองงาม</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>โยดา</t>
+          <t>โซจู</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3608,7 +3690,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3618,44 +3700,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DRX-69</t>
+          <t>DRX-163</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>690043-1</t>
+          <t>690056-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>รื่นรมย์ เหรียญทอง</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>สองสี</t>
+          <t>เฉาก๊วย</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3665,44 +3747,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DRX-81</t>
+          <t>DRX-164</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>690039-1</t>
+          <t>690056-3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>อาร์ม</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>สาคู</t>
+          <t>พาดกลอน</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3712,29 +3794,29 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DRX-85</t>
+          <t>DRX-174</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>690026-2</t>
+          <t>690056-4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ญานิศา แรงจันทร์</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ชิโร่ (แพคเกจวัคซีน)</t>
+          <t>บี1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3744,12 +3826,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3759,44 +3841,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DRX-87</t>
+          <t>DRX-180</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>690056-1</t>
+          <t>690042-2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>วราฤทธิ์ บัวโต</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ไอโชค</t>
+          <t>ดั๊ก</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>โรงพยาบาลสัตว์หมาแมวเลิฟลี่</t>
+          <t>นารีรัตน์ ผลทิพย์</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก (BVT,DW)</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3806,29 +3888,29 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DRX-110</t>
+          <t>DRX-172</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>690067-1</t>
+          <t>690056-5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ไก่</t>
+          <t>อรธิมา เอกจีน</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>อั่งเปา</t>
+          <t>บี2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3843,7 +3925,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3853,29 +3935,29 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DRX-117</t>
+          <t>DRX-191</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>690072-1</t>
+          <t>690009-6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ปิ่นแก้ว</t>
+          <t>ธนาวดี เมธา</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>มาโร</t>
+          <t>ปลาหมึก</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3890,7 +3972,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3900,29 +3982,29 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DRX-126</t>
+          <t>DRX-210</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>690076-1</t>
+          <t>690064-2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>อรพรรณ  ขำสุวรรณ</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>น้องถุงเงิน</t>
+          <t>พลูโต</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3937,7 +4019,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3947,29 +4029,29 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DRX-142</t>
+          <t>DRX-211</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>690082-1</t>
+          <t>690064-3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ประชุม คุณท้าวเทียม</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>มีบุญ</t>
+          <t>ชาแนล</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3979,12 +4061,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3994,29 +4076,29 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DRX-151</t>
+          <t>DRX-212</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>690096-1</t>
+          <t>690064-4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>กฤตยา วิเชียรพาย</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ซาร่า</t>
+          <t>เนปจูน</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4031,7 +4113,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4041,29 +4123,29 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DRX-161</t>
+          <t>DRX-214</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>690100-1</t>
+          <t>690064-6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>พิสิทธิ์    สามกองงาม</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>กิมจิ</t>
+          <t>กาแฟ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4073,12 +4155,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4088,29 +4170,29 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DRX-159</t>
+          <t>DRX-209</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>690100-2</t>
+          <t>690064-1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>พิสิทธิ์    สามกองงาม</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>โซจู</t>
+          <t>ลาคอส</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4120,12 +4202,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4135,29 +4217,29 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DRX-163</t>
+          <t>DRX-213</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>690056-2</t>
+          <t>690064-5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>จีรวรรณ มณีโชติ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>เฉาก๊วย</t>
+          <t>ปลาวาฬ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4172,7 +4254,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4182,29 +4264,29 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DRX-164</t>
+          <t>DRX-218</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>690056-3</t>
+          <t>690122-1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>วิทวัส ศรีลำไย</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>พาดกลอน</t>
+          <t>โอริโอ้</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4214,12 +4296,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4229,44 +4311,44 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DRX-174</t>
+          <t>DRX-229</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>690056-4</t>
+          <t>690127-1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>อรธิมา เอกจีน</t>
+          <t>เจนจิรา</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>บี1</t>
+          <t>จัสติน</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
+          <t>เบญจมาศ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ (DW)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4276,289 +4358,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>DRX-180</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>690042-2</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>วราฤทธิ์ บัวโต</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ดั๊ก</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>DRX-172</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>690056-5</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>อรธิมา เอกจีน</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>บี2</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>DRX-191</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>690009-6</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>ธนาวดี เมธา</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>ปลาหมึก</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>DRX-210</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>690064-2</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>จีรวรรณ มณีโชติ</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>พลูโต</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>DRX-211</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>690064-3</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>จีรวรรณ มณีโชติ</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ชาแนล</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>DRX-212</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>690064-4</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>จีรวรรณ มณีโชติ</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>เนปจูน</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>นารีรัตน์ ผลทิพย์</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>drx</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-05-26 20:36:12</t>
+          <t>2026-05-27 20:15:06</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6749,7 +6549,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6794,7 +6594,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6839,7 +6639,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6884,7 +6684,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6929,7 +6729,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -7084,7 +6884,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7129,7 +6929,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NoLine</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7758,6 +7558,331 @@
         </is>
       </c>
       <c r="P63" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>10037</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>690171-2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ไดม่อน</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (3/3) + พิษสุนัขบ้า (2/2)) / ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>10038</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>690171-1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>สุดารัตน์ โพธิ์ทอง</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ดราก้อน (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ,หยอดยา/รับยา/ป้อนยา/ฉีดยาป้องกันปรสิตภายนอก / ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) +  พิษสุนัขบ้า (1/2))</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>10039</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>690178-1</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ณิชจิรา เติมสินสวัสดิ์</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>มะยม (แพคเกจวัคซีน)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ถ่ายพยาธิ / ฉีดวัคซีน — วัคซีนพิษสุนัขบ้า,วัคซีนไข้หัดและหวัดแมว (ไข้หัด (2/3) + พิษสุนัขบ้า (2/2))</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>10040</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>690284-1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>จันทนี เซี่ยงคิ้ว</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ชานม</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>สัตวแพทย์</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ,รับยาต่อเนื่อง</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Ue95e6b9adfedfe87453d8d88c805be9a</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:00:03</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>10041</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>690136-1</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ลูกนัท</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>มีอาร์</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>สัตวแพทย์</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (+/- กระตุ้นวัคซีน รวม2/2 + RV2/2)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>10042</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>690298-1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>กรรณิการ์ วุฒิกุล</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>มาตังค์</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (ตาบวม)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>drx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>10043</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>690152-4</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ปวริศ มากสอน</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>บีน่า</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>นารีรัตน์ ผลทิพย์</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ตรวจทั่วไป — ดูอาการ (เท้าบวม)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>NoLine</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>drx</t>
         </is>
@@ -7785,7 +7910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12182,6 +12307,692 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:08</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>DRX:67</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Ud4b955ac4ddd56e12f2ab3cbc77f790b</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:10</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>690001-1</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Ub52a3ad9704e3f5c3194c5cf96875084</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>690224-1</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>U319ce6867f8c2e421e72170330fca9ce</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:12</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>690287-2</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>U12d49c2dfd70e222ff4d4e5febe9a27a</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>690165-1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>U767d6bba954a02bc3bd47fa2156cefb2</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:14</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>690284-1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ue95e6b9adfedfe87453d8d88c805be9a</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:15</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>690291-1</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>U85ffc0c0ed720e5aa118f80fe81e4f51</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:16</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>690131-2</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ud3199338d71e5f310af197255682ff41</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:17</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>690157-1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>U9d5f25862cbd9d2fe2c58bb5ba7c532f</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>690118-1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ub741455c24a2afcee792ea9d8af87077</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:18</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>690160-2</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>U4641000ef0dc24781745999e95de3998</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:19</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>690289-1</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>U7cc0f7ce8f6e545e67c7e77aa35db9ce</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>690299-3</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:21</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>690084-2</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:22</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>690189-1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>U5d220d047421251dbe36331d61631e3a</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:23</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>690201-1</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>U835cf6a27aa276bd81a80630f363998b</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>updated</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:05:25</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Queue_Build</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Queue+0</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:30:16</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>690299-1</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>U47aa79494e18e479471bae5f420f8caf</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>sibling HN → บราวนี่</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-27 12:30:25</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>DRX:67</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-27 13:00:02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Queue_Build</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Queue+7</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-27 20:15:12</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>RegisterSibling</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>690084-3</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>U22ef391387145f0f1cfd0889a2e437f9</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>sibling HN → ชาไทย</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-27 20:15:22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>DRX_Sync</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>DRX:61</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
